--- a/data/trans_orig/MCS12_SP-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud mental (SF12)</t>
+          <t>Puntuación media del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,29; 51,39</t>
+          <t>50,3; 51,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,82; 51,1</t>
+          <t>49,85; 51,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,37; 51,62</t>
+          <t>50,35; 51,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,77; 51,27</t>
+          <t>49,86; 51,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,38; 50,45</t>
+          <t>49,4; 50,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,56; 47,85</t>
+          <t>46,6; 47,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,11; 48,64</t>
+          <t>47,06; 48,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,07; 48,42</t>
+          <t>47,07; 48,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,98; 50,71</t>
+          <t>49,92; 50,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,07; 49,01</t>
+          <t>48,11; 49,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,68; 49,71</t>
+          <t>48,7; 49,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,31; 49,37</t>
+          <t>48,31; 49,41</t>
         </is>
       </c>
     </row>
@@ -856,47 +856,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,03; 53,65</t>
+          <t>53,07; 53,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,21; 52,86</t>
+          <t>52,15; 52,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,41; 53,07</t>
+          <t>52,42; 53,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,84; 53,85</t>
+          <t>52,87; 53,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,88; 51,65</t>
+          <t>50,84; 51,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,56; 50,47</t>
+          <t>49,54; 50,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,07; 51,86</t>
+          <t>51,14; 51,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,06; 51,85</t>
+          <t>49,17; 51,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,11; 52,59</t>
+          <t>52,08; 52,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,88; 52,41</t>
+          <t>51,87; 52,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,0; 52,72</t>
+          <t>50,84; 52,67</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,69; 53,86</t>
+          <t>52,71; 53,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,52; 53,88</t>
+          <t>52,43; 53,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,7; 53,82</t>
+          <t>52,64; 53,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,14; 53,47</t>
+          <t>52,15; 53,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,78; 52,2</t>
+          <t>50,77; 52,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,3; 52,75</t>
+          <t>51,31; 52,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,76; 53,02</t>
+          <t>51,74; 52,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,14; 52,31</t>
+          <t>51,13; 52,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,96; 52,87</t>
+          <t>52,03; 52,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,14; 53,15</t>
+          <t>52,17; 53,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 53,24</t>
+          <t>52,36; 53,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,9; 52,76</t>
+          <t>51,87; 52,76</t>
         </is>
       </c>
     </row>
@@ -1136,52 +1136,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,31; 52,8</t>
+          <t>52,27; 52,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,76; 52,35</t>
+          <t>51,79; 52,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,16; 52,69</t>
+          <t>52,15; 52,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,37</t>
+          <t>52,47; 53,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,07</t>
+          <t>50,45; 51,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,85; 49,57</t>
+          <t>48,86; 49,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,28; 50,91</t>
+          <t>50,26; 50,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,31; 50,92</t>
+          <t>49,38; 50,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,45; 51,86</t>
+          <t>51,47; 51,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,38; 50,84</t>
+          <t>50,36; 50,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,9; 51,94</t>
+          <t>50,84; 51,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50,58</t>
+          <t>50,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,7</t>
+          <t>47,68</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,87</t>
+          <t>48,99</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,3; 51,41</t>
+          <t>50,27; 51,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,85; 51,02</t>
+          <t>49,83; 51,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,35; 51,59</t>
+          <t>50,32; 51,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,86; 51,4</t>
+          <t>50,04; 51,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>49,4; 50,41</t>
+          <t>49,35; 50,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,6; 47,89</t>
+          <t>46,59; 47,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,06; 48,63</t>
+          <t>46,99; 48,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>47,07; 48,38</t>
+          <t>47,06; 48,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49,92; 50,68</t>
+          <t>49,96; 50,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48,11; 49,06</t>
+          <t>48,12; 49,04</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48,7; 49,68</t>
+          <t>48,64; 49,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,31; 49,41</t>
+          <t>48,52; 49,45</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,3</t>
+          <t>53,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,98</t>
+          <t>51,48</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,15</t>
+          <t>52,25</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>53,07; 53,63</t>
+          <t>53,08; 53,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,15; 52,84</t>
+          <t>52,2; 52,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,42; 53,07</t>
+          <t>52,43; 53,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,87; 53,88</t>
+          <t>52,58; 53,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,84; 51,66</t>
+          <t>50,82; 51,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,54; 50,5</t>
+          <t>49,58; 50,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,14; 51,88</t>
+          <t>51,09; 51,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>49,17; 51,79</t>
+          <t>51,09; 51,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>52,08; 52,6</t>
+          <t>52,08; 52,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,06; 51,64</t>
+          <t>51,06; 51,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,87; 52,38</t>
+          <t>51,88; 52,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,84; 52,67</t>
+          <t>51,99; 52,51</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,91</t>
+          <t>52,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,78</t>
+          <t>51,62</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,33</t>
+          <t>52,28</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 53,81</t>
+          <t>52,68; 53,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,43; 53,86</t>
+          <t>52,52; 53,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,64; 53,79</t>
+          <t>52,66; 53,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,15; 53,5</t>
+          <t>52,3; 53,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,77; 52,2</t>
+          <t>50,71; 52,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,31; 52,74</t>
+          <t>51,3; 52,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,74; 52,96</t>
+          <t>51,7; 52,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,13; 52,33</t>
+          <t>50,98; 52,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52,03; 52,92</t>
+          <t>51,97; 52,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,17; 53,16</t>
+          <t>52,16; 53,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52,36; 53,19</t>
+          <t>52,4; 53,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,87; 52,76</t>
+          <t>51,84; 52,67</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,82</t>
+          <t>52,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,45</t>
+          <t>50,68</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,6</t>
+          <t>51,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,27; 52,77</t>
+          <t>52,29; 52,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,79; 52,33</t>
+          <t>51,77; 52,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,15; 52,7</t>
+          <t>52,17; 52,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52,47; 53,32</t>
+          <t>52,34; 52,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,07</t>
+          <t>50,46; 51,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,86; 49,54</t>
+          <t>48,9; 49,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,26; 50,93</t>
+          <t>50,28; 50,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,38; 50,93</t>
+          <t>50,38; 50,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,82</t>
+          <t>51,46; 51,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50,36; 50,82</t>
+          <t>50,4; 50,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,27; 51,71</t>
+          <t>51,29; 51,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,84; 51,98</t>
+          <t>51,41; 51,83</t>
         </is>
       </c>
     </row>
